--- a/mom/docs/forms/frm-600-inspection/FRM-656_Concession_Deviation_Permit_Request.xlsx
+++ b/mom/docs/forms/frm-600-inspection/FRM-656_Concession_Deviation_Permit_Request.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -501,6 +501,12 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
       <color rgb="00CBD5E1"/>
       <sz val="8"/>
     </font>
@@ -510,7 +516,7 @@
       <sz val="6"/>
     </font>
   </fonts>
-  <fills count="53">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
@@ -778,6 +784,12 @@
         <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="264">
     <border>
@@ -3737,7 +3749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="528">
+  <cellXfs count="529">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4979,10 +4991,13 @@
     <xf numFmtId="0" fontId="80" fillId="52" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="84" fillId="53" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="260" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="51" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="84" fillId="53" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="52" borderId="259" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5000,7 +5015,7 @@
     <xf numFmtId="0" fontId="79" fillId="49" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="47" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5008,7 +5023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="86" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5121,6 +5136,52 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số giấy phép
+Mã duy nhất của đơn xin nhân nhượng / sai lệch.</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Số lượng ảnh hưởng
+Số chi tiết nằm trong phạm vi xin phép.</t>
+      </text>
+    </comment>
+    <comment ref="U11" authorId="0" shapeId="0">
+      <text>
+        <t>Số NCR
+FRM-651 liên quan.</t>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0">
+      <text>
+        <t>Loại nhân nhượng
+Use-as-is = dùng nguyên trạng · Repair = sửa · Production permit = cho phép sai lệch trước sản xuất.</t>
+      </text>
+    </comment>
+    <comment ref="U21" authorId="0" shapeId="0">
+      <text>
+        <t>Hiệu lực
+Giới hạn số lượng hoặc thời hạn áp dụng.</t>
+      </text>
+    </comment>
+    <comment ref="AF30" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS = không ảnh hưởng · HOLD = cần xem xét thêm · FAIL = ảnh hưởng đáng kể.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5445,7 +5506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:BS48"/>
+  <dimension ref="A2:AN48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.375" customWidth="1" style="264" min="1" max="1"/>
@@ -5691,7 +5752,7 @@
       <c r="AN6" s="272" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="527" t="n"/>
+      <c r="A7" s="528" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -5979,7 +6040,7 @@
       <c r="AN12" s="493" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1" s="264">
-      <c r="A13" s="527" t="n"/>
+      <c r="A13" s="528" t="n"/>
       <c r="B13" s="26" t="n"/>
       <c r="C13" s="26" t="n"/>
       <c r="D13" s="26" t="n"/>
@@ -6069,7 +6130,7 @@
     <row r="15" ht="17" customHeight="1" s="264">
       <c r="A15" s="494" t="inlineStr">
         <is>
-          <t>NONCONFORMANCE DESCRIPTION</t>
+          <t>Describe the nonconformance, the affected characteristic and the actual condition.</t>
         </is>
       </c>
       <c r="B15" s="474" t="n"/>
@@ -6239,7 +6300,7 @@
       <c r="AN18" s="493" t="n"/>
     </row>
     <row r="19" ht="4" customHeight="1" s="264">
-      <c r="A19" s="527" t="n"/>
+      <c r="A19" s="528" t="n"/>
       <c r="B19" s="26" t="n"/>
       <c r="C19" s="26" t="n"/>
       <c r="D19" s="26" t="n"/>
@@ -6377,7 +6438,7 @@
       <c r="AN21" s="472" t="n"/>
     </row>
     <row r="22" ht="4" customHeight="1" s="264">
-      <c r="A22" s="527" t="n"/>
+      <c r="A22" s="528" t="n"/>
       <c r="B22" s="26" t="n"/>
       <c r="C22" s="26" t="n"/>
       <c r="D22" s="26" t="n"/>
@@ -6467,7 +6528,7 @@
     <row r="24" ht="17" customHeight="1" s="264">
       <c r="A24" s="494" t="inlineStr">
         <is>
-          <t>TECHNICAL JUSTIFICATION</t>
+          <t>Why the deviation is acceptable: engineering rationale, supporting analysis or test.</t>
         </is>
       </c>
       <c r="B24" s="474" t="n"/>
@@ -6637,7 +6698,7 @@
       <c r="AN27" s="493" t="n"/>
     </row>
     <row r="28" ht="4" customHeight="1" s="264">
-      <c r="A28" s="527" t="n"/>
+      <c r="A28" s="528" t="n"/>
       <c r="B28" s="26" t="n"/>
       <c r="C28" s="26" t="n"/>
       <c r="D28" s="26" t="n"/>
@@ -6902,9 +6963,9 @@
         <v/>
       </c>
       <c r="B33" s="482" t="n"/>
-      <c r="C33" s="507" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C33" s="513" t="inlineStr">
+        <is>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D33" s="481" t="n"/>
@@ -6955,9 +7016,9 @@
         <v/>
       </c>
       <c r="B34" s="482" t="n"/>
-      <c r="C34" s="507" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C34" s="513" t="inlineStr">
+        <is>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D34" s="481" t="n"/>
@@ -7008,9 +7069,9 @@
         <v/>
       </c>
       <c r="B35" s="482" t="n"/>
-      <c r="C35" s="507" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C35" s="513" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D35" s="481" t="n"/>
@@ -7056,19 +7117,19 @@
       <c r="AN35" s="486" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="264">
-      <c r="A36" s="513">
+      <c r="A36" s="514">
         <f>ROW()-ROW($A$31)+1</f>
         <v/>
       </c>
       <c r="B36" s="489" t="n"/>
-      <c r="C36" s="514" t="inlineStr">
-        <is>
-          <t>QUA</t>
+      <c r="C36" s="515" t="inlineStr">
+        <is>
+          <t>OPS</t>
         </is>
       </c>
       <c r="D36" s="488" t="n"/>
       <c r="E36" s="489" t="n"/>
-      <c r="F36" s="515" t="inlineStr">
+      <c r="F36" s="516" t="inlineStr">
         <is>
           <t>Containment of remaining stock / WIP.</t>
         </is>
@@ -7088,7 +7149,7 @@
       <c r="S36" s="488" t="n"/>
       <c r="T36" s="488" t="n"/>
       <c r="U36" s="489" t="n"/>
-      <c r="V36" s="516" t="inlineStr"/>
+      <c r="V36" s="517" t="inlineStr"/>
       <c r="W36" s="488" t="n"/>
       <c r="X36" s="488" t="n"/>
       <c r="Y36" s="488" t="n"/>
@@ -7098,18 +7159,18 @@
       <c r="AC36" s="488" t="n"/>
       <c r="AD36" s="488" t="n"/>
       <c r="AE36" s="489" t="n"/>
-      <c r="AF36" s="517" t="n"/>
+      <c r="AF36" s="518" t="n"/>
       <c r="AG36" s="488" t="n"/>
       <c r="AH36" s="488" t="n"/>
       <c r="AI36" s="489" t="n"/>
-      <c r="AJ36" s="518" t="n"/>
+      <c r="AJ36" s="519" t="n"/>
       <c r="AK36" s="488" t="n"/>
       <c r="AL36" s="488" t="n"/>
       <c r="AM36" s="488" t="n"/>
       <c r="AN36" s="493" t="n"/>
     </row>
     <row r="37" ht="4" customHeight="1" s="264">
-      <c r="A37" s="527" t="n"/>
+      <c r="A37" s="528" t="n"/>
       <c r="B37" s="26" t="n"/>
       <c r="C37" s="26" t="n"/>
       <c r="D37" s="26" t="n"/>
@@ -7297,7 +7358,7 @@
       <c r="AN40" s="493" t="n"/>
     </row>
     <row r="41" ht="4" customHeight="1" s="264">
-      <c r="A41" s="527" t="n"/>
+      <c r="A41" s="528" t="n"/>
       <c r="B41" s="26" t="n"/>
       <c r="C41" s="26" t="n"/>
       <c r="D41" s="26" t="n"/>
@@ -7385,7 +7446,7 @@
       <c r="AN42" s="472" t="n"/>
     </row>
     <row r="43" ht="17" customHeight="1" s="264">
-      <c r="A43" s="519" t="inlineStr">
+      <c r="A43" s="520" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
@@ -7402,7 +7463,7 @@
       <c r="K43" s="471" t="n"/>
       <c r="L43" s="471" t="n"/>
       <c r="M43" s="472" t="n"/>
-      <c r="N43" s="519" t="inlineStr">
+      <c r="N43" s="520" t="inlineStr">
         <is>
           <t>QA Manager</t>
         </is>
@@ -7419,7 +7480,7 @@
       <c r="X43" s="471" t="n"/>
       <c r="Y43" s="471" t="n"/>
       <c r="Z43" s="472" t="n"/>
-      <c r="AA43" s="519" t="inlineStr">
+      <c r="AA43" s="520" t="inlineStr">
         <is>
           <t>Customer / Authority</t>
         </is>
@@ -7439,69 +7500,69 @@
       <c r="AN43" s="472" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1" s="264">
-      <c r="A44" s="520" t="inlineStr">
+      <c r="A44" s="521" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B44" s="521" t="n"/>
-      <c r="C44" s="521" t="n"/>
-      <c r="D44" s="521" t="n"/>
-      <c r="E44" s="521" t="n"/>
-      <c r="F44" s="521" t="n"/>
-      <c r="G44" s="521" t="n"/>
-      <c r="H44" s="521" t="n"/>
-      <c r="I44" s="521" t="n"/>
-      <c r="J44" s="521" t="n"/>
-      <c r="K44" s="521" t="n"/>
-      <c r="L44" s="521" t="n"/>
-      <c r="M44" s="522" t="n"/>
-      <c r="N44" s="520" t="inlineStr">
+      <c r="B44" s="522" t="n"/>
+      <c r="C44" s="522" t="n"/>
+      <c r="D44" s="522" t="n"/>
+      <c r="E44" s="522" t="n"/>
+      <c r="F44" s="522" t="n"/>
+      <c r="G44" s="522" t="n"/>
+      <c r="H44" s="522" t="n"/>
+      <c r="I44" s="522" t="n"/>
+      <c r="J44" s="522" t="n"/>
+      <c r="K44" s="522" t="n"/>
+      <c r="L44" s="522" t="n"/>
+      <c r="M44" s="523" t="n"/>
+      <c r="N44" s="521" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="O44" s="521" t="n"/>
-      <c r="P44" s="521" t="n"/>
-      <c r="Q44" s="521" t="n"/>
-      <c r="R44" s="521" t="n"/>
-      <c r="S44" s="521" t="n"/>
-      <c r="T44" s="521" t="n"/>
-      <c r="U44" s="521" t="n"/>
-      <c r="V44" s="521" t="n"/>
-      <c r="W44" s="521" t="n"/>
-      <c r="X44" s="521" t="n"/>
-      <c r="Y44" s="521" t="n"/>
-      <c r="Z44" s="522" t="n"/>
-      <c r="AA44" s="520" t="inlineStr">
+      <c r="O44" s="522" t="n"/>
+      <c r="P44" s="522" t="n"/>
+      <c r="Q44" s="522" t="n"/>
+      <c r="R44" s="522" t="n"/>
+      <c r="S44" s="522" t="n"/>
+      <c r="T44" s="522" t="n"/>
+      <c r="U44" s="522" t="n"/>
+      <c r="V44" s="522" t="n"/>
+      <c r="W44" s="522" t="n"/>
+      <c r="X44" s="522" t="n"/>
+      <c r="Y44" s="522" t="n"/>
+      <c r="Z44" s="523" t="n"/>
+      <c r="AA44" s="521" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AB44" s="521" t="n"/>
-      <c r="AC44" s="521" t="n"/>
-      <c r="AD44" s="521" t="n"/>
-      <c r="AE44" s="521" t="n"/>
-      <c r="AF44" s="521" t="n"/>
-      <c r="AG44" s="521" t="n"/>
-      <c r="AH44" s="521" t="n"/>
-      <c r="AI44" s="521" t="n"/>
-      <c r="AJ44" s="521" t="n"/>
-      <c r="AK44" s="521" t="n"/>
-      <c r="AL44" s="521" t="n"/>
-      <c r="AM44" s="521" t="n"/>
-      <c r="AN44" s="522" t="n"/>
+      <c r="AB44" s="522" t="n"/>
+      <c r="AC44" s="522" t="n"/>
+      <c r="AD44" s="522" t="n"/>
+      <c r="AE44" s="522" t="n"/>
+      <c r="AF44" s="522" t="n"/>
+      <c r="AG44" s="522" t="n"/>
+      <c r="AH44" s="522" t="n"/>
+      <c r="AI44" s="522" t="n"/>
+      <c r="AJ44" s="522" t="n"/>
+      <c r="AK44" s="522" t="n"/>
+      <c r="AL44" s="522" t="n"/>
+      <c r="AM44" s="522" t="n"/>
+      <c r="AN44" s="523" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="264">
-      <c r="A45" s="523" t="n"/>
-      <c r="M45" s="524" t="n"/>
-      <c r="N45" s="523" t="n"/>
-      <c r="Z45" s="524" t="n"/>
-      <c r="AA45" s="523" t="n"/>
-      <c r="AN45" s="524" t="n"/>
+      <c r="A45" s="524" t="n"/>
+      <c r="M45" s="525" t="n"/>
+      <c r="N45" s="524" t="n"/>
+      <c r="Z45" s="525" t="n"/>
+      <c r="AA45" s="524" t="n"/>
+      <c r="AN45" s="525" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1" s="264">
-      <c r="A46" s="525" t="n"/>
+      <c r="A46" s="526" t="n"/>
       <c r="B46" s="488" t="n"/>
       <c r="C46" s="488" t="n"/>
       <c r="D46" s="488" t="n"/>
@@ -7514,7 +7575,7 @@
       <c r="K46" s="488" t="n"/>
       <c r="L46" s="488" t="n"/>
       <c r="M46" s="493" t="n"/>
-      <c r="N46" s="525" t="n"/>
+      <c r="N46" s="526" t="n"/>
       <c r="O46" s="488" t="n"/>
       <c r="P46" s="488" t="n"/>
       <c r="Q46" s="488" t="n"/>
@@ -7527,7 +7588,7 @@
       <c r="X46" s="488" t="n"/>
       <c r="Y46" s="488" t="n"/>
       <c r="Z46" s="493" t="n"/>
-      <c r="AA46" s="525" t="n"/>
+      <c r="AA46" s="526" t="n"/>
       <c r="AB46" s="488" t="n"/>
       <c r="AC46" s="488" t="n"/>
       <c r="AD46" s="488" t="n"/>
@@ -7543,7 +7604,7 @@
       <c r="AN46" s="493" t="n"/>
     </row>
     <row r="47" ht="4" customHeight="1" s="264">
-      <c r="A47" s="527" t="n"/>
+      <c r="A47" s="528" t="n"/>
       <c r="B47" s="26" t="n"/>
       <c r="C47" s="26" t="n"/>
       <c r="D47" s="26" t="n"/>
@@ -7585,9 +7646,9 @@
       <c r="AN47" s="26" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1" s="264">
-      <c r="A48" s="526" t="inlineStr">
-        <is>
-          <t>NOTICE — A concession authorises use or shipment of nonconforming product only within the stated limits. Customer approval is mandatory where the contract or specification requires it. Ref: SOP-505 / ISO 9001 §8.7. Retain: 10 years.</t>
+      <c r="A48" s="527" t="inlineStr">
+        <is>
+          <t>NOTICE — A concession authorises use or shipment of nonconforming product only within the stated limits. Customer approval is mandatory where the contract or specification requires it. Ref: SOP-505 / ISO 9001 §8.7. Retain: 10 years. Enter data only in white input cells. Do not add, delete or resize columns/rows.</t>
         </is>
       </c>
       <c r="B48" s="471" t="n"/>
@@ -7766,6 +7827,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
